--- a/v.6.4.2/test_data/total_latest.xlsx
+++ b/v.6.4.2/test_data/total_latest.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1008"/>
+  <dimension ref="A1:M1015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40889,7 +40889,7 @@
         <v>46279</v>
       </c>
       <c r="B987" t="n">
-        <v>32921</v>
+        <v>32919</v>
       </c>
       <c r="C987" t="n">
         <v>6217</v>
@@ -40916,7 +40916,7 @@
         <v>881</v>
       </c>
       <c r="K987" t="n">
-        <v>5268</v>
+        <v>5266</v>
       </c>
       <c r="L987" t="n">
         <v>10708</v>
@@ -40930,7 +40930,7 @@
         <v>46280</v>
       </c>
       <c r="B988" t="n">
-        <v>31245</v>
+        <v>31243</v>
       </c>
       <c r="C988" t="n">
         <v>5911</v>
@@ -40957,7 +40957,7 @@
         <v>901</v>
       </c>
       <c r="K988" t="n">
-        <v>4571</v>
+        <v>4569</v>
       </c>
       <c r="L988" t="n">
         <v>11357</v>
@@ -40971,7 +40971,7 @@
         <v>46281</v>
       </c>
       <c r="B989" t="n">
-        <v>32239</v>
+        <v>32237</v>
       </c>
       <c r="C989" t="n">
         <v>6539</v>
@@ -40998,7 +40998,7 @@
         <v>969</v>
       </c>
       <c r="K989" t="n">
-        <v>3807</v>
+        <v>3805</v>
       </c>
       <c r="L989" t="n">
         <v>12547</v>
@@ -41012,7 +41012,7 @@
         <v>46282</v>
       </c>
       <c r="B990" t="n">
-        <v>32321</v>
+        <v>32319</v>
       </c>
       <c r="C990" t="n">
         <v>7941</v>
@@ -41039,7 +41039,7 @@
         <v>967</v>
       </c>
       <c r="K990" t="n">
-        <v>3207</v>
+        <v>3205</v>
       </c>
       <c r="L990" t="n">
         <v>14746</v>
@@ -41053,7 +41053,7 @@
         <v>46283</v>
       </c>
       <c r="B991" t="n">
-        <v>30284</v>
+        <v>30282</v>
       </c>
       <c r="C991" t="n">
         <v>7851</v>
@@ -41080,7 +41080,7 @@
         <v>985</v>
       </c>
       <c r="K991" t="n">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="L991" t="n">
         <v>14433</v>
@@ -41094,7 +41094,7 @@
         <v>46284</v>
       </c>
       <c r="B992" t="n">
-        <v>17663</v>
+        <v>17661</v>
       </c>
       <c r="C992" t="n">
         <v>3699</v>
@@ -41121,13 +41121,13 @@
         <v>743</v>
       </c>
       <c r="K992" t="n">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="L992" t="n">
         <v>8111</v>
       </c>
       <c r="M992" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="993">
@@ -41135,7 +41135,7 @@
         <v>46285</v>
       </c>
       <c r="B993" t="n">
-        <v>25237</v>
+        <v>25235</v>
       </c>
       <c r="C993" t="n">
         <v>5658</v>
@@ -41162,13 +41162,13 @@
         <v>971</v>
       </c>
       <c r="K993" t="n">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="L993" t="n">
         <v>9368</v>
       </c>
       <c r="M993" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="994">
@@ -41176,7 +41176,7 @@
         <v>46286</v>
       </c>
       <c r="B994" t="n">
-        <v>33074</v>
+        <v>33072</v>
       </c>
       <c r="C994" t="n">
         <v>7254</v>
@@ -41203,7 +41203,7 @@
         <v>944</v>
       </c>
       <c r="K994" t="n">
-        <v>3800</v>
+        <v>3798</v>
       </c>
       <c r="L994" t="n">
         <v>12397</v>
@@ -41217,7 +41217,7 @@
         <v>46287</v>
       </c>
       <c r="B995" t="n">
-        <v>31269</v>
+        <v>31267</v>
       </c>
       <c r="C995" t="n">
         <v>7455</v>
@@ -41244,7 +41244,7 @@
         <v>910</v>
       </c>
       <c r="K995" t="n">
-        <v>3660</v>
+        <v>3658</v>
       </c>
       <c r="L995" t="n">
         <v>14113</v>
@@ -41258,7 +41258,7 @@
         <v>46288</v>
       </c>
       <c r="B996" t="n">
-        <v>28359</v>
+        <v>28357</v>
       </c>
       <c r="C996" t="n">
         <v>8711</v>
@@ -41285,7 +41285,7 @@
         <v>1114</v>
       </c>
       <c r="K996" t="n">
-        <v>3295</v>
+        <v>3293</v>
       </c>
       <c r="L996" t="n">
         <v>15282</v>
@@ -41299,7 +41299,7 @@
         <v>46289</v>
       </c>
       <c r="B997" t="n">
-        <v>9284</v>
+        <v>9282</v>
       </c>
       <c r="C997" t="n">
         <v>16</v>
@@ -41326,13 +41326,13 @@
         <v>702</v>
       </c>
       <c r="K997" t="n">
-        <v>3196</v>
+        <v>3194</v>
       </c>
       <c r="L997" t="n">
         <v>27</v>
       </c>
       <c r="M997" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="998">
@@ -41340,7 +41340,7 @@
         <v>46291</v>
       </c>
       <c r="B998" t="n">
-        <v>9122</v>
+        <v>9120</v>
       </c>
       <c r="C998" t="n">
         <v>13</v>
@@ -41367,13 +41367,13 @@
         <v>110</v>
       </c>
       <c r="K998" t="n">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="L998" t="n">
         <v>17</v>
       </c>
       <c r="M998" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="999">
@@ -41381,7 +41381,7 @@
         <v>46292</v>
       </c>
       <c r="B999" t="n">
-        <v>19933</v>
+        <v>19931</v>
       </c>
       <c r="C999" t="n">
         <v>5838</v>
@@ -41408,13 +41408,13 @@
         <v>395</v>
       </c>
       <c r="K999" t="n">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="L999" t="n">
         <v>8902</v>
       </c>
       <c r="M999" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1000">
@@ -41422,7 +41422,7 @@
         <v>46293</v>
       </c>
       <c r="B1000" t="n">
-        <v>31780</v>
+        <v>31778</v>
       </c>
       <c r="C1000" t="n">
         <v>7700</v>
@@ -41449,7 +41449,7 @@
         <v>618</v>
       </c>
       <c r="K1000" t="n">
-        <v>3545</v>
+        <v>3543</v>
       </c>
       <c r="L1000" t="n">
         <v>12599</v>
@@ -41463,7 +41463,7 @@
         <v>46294</v>
       </c>
       <c r="B1001" t="n">
-        <v>33845</v>
+        <v>33843</v>
       </c>
       <c r="C1001" t="n">
         <v>6910</v>
@@ -41490,7 +41490,7 @@
         <v>721</v>
       </c>
       <c r="K1001" t="n">
-        <v>2996</v>
+        <v>2994</v>
       </c>
       <c r="L1001" t="n">
         <v>17865</v>
@@ -41504,7 +41504,7 @@
         <v>46295</v>
       </c>
       <c r="B1002" t="n">
-        <v>29391</v>
+        <v>29389</v>
       </c>
       <c r="C1002" t="n">
         <v>4962</v>
@@ -41531,7 +41531,7 @@
         <v>825</v>
       </c>
       <c r="K1002" t="n">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="L1002" t="n">
         <v>14097</v>
@@ -41545,7 +41545,7 @@
         <v>46296</v>
       </c>
       <c r="B1003" t="n">
-        <v>39774</v>
+        <v>39772</v>
       </c>
       <c r="C1003" t="n">
         <v>7154</v>
@@ -41572,7 +41572,7 @@
         <v>768</v>
       </c>
       <c r="K1003" t="n">
-        <v>4061</v>
+        <v>4059</v>
       </c>
       <c r="L1003" t="n">
         <v>19426</v>
@@ -41586,7 +41586,7 @@
         <v>46297</v>
       </c>
       <c r="B1004" t="n">
-        <v>36067</v>
+        <v>36064</v>
       </c>
       <c r="C1004" t="n">
         <v>7778</v>
@@ -41613,7 +41613,7 @@
         <v>654</v>
       </c>
       <c r="K1004" t="n">
-        <v>4749</v>
+        <v>4746</v>
       </c>
       <c r="L1004" t="n">
         <v>18943</v>
@@ -41627,7 +41627,7 @@
         <v>46298</v>
       </c>
       <c r="B1005" t="n">
-        <v>25225</v>
+        <v>25223</v>
       </c>
       <c r="C1005" t="n">
         <v>6502</v>
@@ -41654,13 +41654,13 @@
         <v>507</v>
       </c>
       <c r="K1005" t="n">
-        <v>2919</v>
+        <v>2917</v>
       </c>
       <c r="L1005" t="n">
         <v>11751</v>
       </c>
       <c r="M1005" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1006">
@@ -41668,7 +41668,7 @@
         <v>46299</v>
       </c>
       <c r="B1006" t="n">
-        <v>30240</v>
+        <v>30238</v>
       </c>
       <c r="C1006" t="n">
         <v>5751</v>
@@ -41695,13 +41695,13 @@
         <v>631</v>
       </c>
       <c r="K1006" t="n">
-        <v>3578</v>
+        <v>3576</v>
       </c>
       <c r="L1006" t="n">
         <v>14730</v>
       </c>
       <c r="M1006" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1007">
@@ -41709,7 +41709,7 @@
         <v>46300</v>
       </c>
       <c r="B1007" t="n">
-        <v>28097</v>
+        <v>28095</v>
       </c>
       <c r="C1007" t="n">
         <v>6344</v>
@@ -41736,7 +41736,7 @@
         <v>737</v>
       </c>
       <c r="K1007" t="n">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="L1007" t="n">
         <v>14307</v>
@@ -41750,13 +41750,13 @@
         <v>46301</v>
       </c>
       <c r="B1008" t="n">
-        <v>35492</v>
+        <v>35486</v>
       </c>
       <c r="C1008" t="n">
         <v>7556</v>
       </c>
       <c r="D1008" t="n">
-        <v>9509</v>
+        <v>9508</v>
       </c>
       <c r="E1008" t="n">
         <v>1606</v>
@@ -41777,13 +41777,300 @@
         <v>826</v>
       </c>
       <c r="K1008" t="n">
-        <v>4404</v>
+        <v>4399</v>
       </c>
       <c r="L1008" t="n">
-        <v>17065</v>
+        <v>17064</v>
       </c>
       <c r="M1008" t="n">
         <v>31</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1009" t="n">
+        <v>32729</v>
+      </c>
+      <c r="C1009" t="n">
+        <v>7744</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>9284</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>892</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>329</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>5579</v>
+      </c>
+      <c r="H1009" t="n">
+        <v>2921</v>
+      </c>
+      <c r="I1009" t="n">
+        <v>2290</v>
+      </c>
+      <c r="J1009" t="n">
+        <v>784</v>
+      </c>
+      <c r="K1009" t="n">
+        <v>2906</v>
+      </c>
+      <c r="L1009" t="n">
+        <v>17028</v>
+      </c>
+      <c r="M1009" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1010" t="n">
+        <v>30867</v>
+      </c>
+      <c r="C1010" t="n">
+        <v>7007</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>9189</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>839</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>273</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>5032</v>
+      </c>
+      <c r="H1010" t="n">
+        <v>2687</v>
+      </c>
+      <c r="I1010" t="n">
+        <v>2426</v>
+      </c>
+      <c r="J1010" t="n">
+        <v>764</v>
+      </c>
+      <c r="K1010" t="n">
+        <v>2650</v>
+      </c>
+      <c r="L1010" t="n">
+        <v>16196</v>
+      </c>
+      <c r="M1010" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1011" t="n">
+        <v>27438</v>
+      </c>
+      <c r="C1011" t="n">
+        <v>6268</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>7915</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>166</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>4976</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>2749</v>
+      </c>
+      <c r="I1011" t="n">
+        <v>2331</v>
+      </c>
+      <c r="J1011" t="n">
+        <v>795</v>
+      </c>
+      <c r="K1011" t="n">
+        <v>2238</v>
+      </c>
+      <c r="L1011" t="n">
+        <v>14183</v>
+      </c>
+      <c r="M1011" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1012" t="n">
+        <v>23970</v>
+      </c>
+      <c r="C1012" t="n">
+        <v>5483</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>6967</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>469</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>350</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>3942</v>
+      </c>
+      <c r="H1012" t="n">
+        <v>2299</v>
+      </c>
+      <c r="I1012" t="n">
+        <v>1961</v>
+      </c>
+      <c r="J1012" t="n">
+        <v>652</v>
+      </c>
+      <c r="K1012" t="n">
+        <v>1847</v>
+      </c>
+      <c r="L1012" t="n">
+        <v>12450</v>
+      </c>
+      <c r="M1012" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1013" t="n">
+        <v>26891</v>
+      </c>
+      <c r="C1013" t="n">
+        <v>5106</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>6046</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>170</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>5563</v>
+      </c>
+      <c r="H1013" t="n">
+        <v>2832</v>
+      </c>
+      <c r="I1013" t="n">
+        <v>2348</v>
+      </c>
+      <c r="J1013" t="n">
+        <v>752</v>
+      </c>
+      <c r="K1013" t="n">
+        <v>4073</v>
+      </c>
+      <c r="L1013" t="n">
+        <v>11152</v>
+      </c>
+      <c r="M1013" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1014" t="n">
+        <v>35396</v>
+      </c>
+      <c r="C1014" t="n">
+        <v>5510</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>9163</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>1133</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>548</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>8232</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>3216</v>
+      </c>
+      <c r="I1014" t="n">
+        <v>2619</v>
+      </c>
+      <c r="J1014" t="n">
+        <v>756</v>
+      </c>
+      <c r="K1014" t="n">
+        <v>4219</v>
+      </c>
+      <c r="L1014" t="n">
+        <v>14673</v>
+      </c>
+      <c r="M1014" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1015" t="n">
+        <v>33427</v>
+      </c>
+      <c r="C1015" t="n">
+        <v>4225</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>10890</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>934</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>529</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>8276</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>2681</v>
+      </c>
+      <c r="I1015" t="n">
+        <v>2249</v>
+      </c>
+      <c r="J1015" t="n">
+        <v>726</v>
+      </c>
+      <c r="K1015" t="n">
+        <v>2917</v>
+      </c>
+      <c r="L1015" t="n">
+        <v>15115</v>
+      </c>
+      <c r="M1015" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
